--- a/MU/Test upload format/SHG/2026 - 2027 - SHG/Q1 26-27  SHG.xlsx
+++ b/MU/Test upload format/SHG/2026 - 2027 - SHG/Q1 26-27  SHG.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1399,7 +1399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:AO21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -1899,7 +1899,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" hidden="1" spans="1:41">
+    <row r="5" s="2" customFormat="1" spans="1:41">
       <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" ht="18" hidden="1" customHeight="1" spans="1:41">
+    <row r="6" s="2" customFormat="1" ht="18" customHeight="1" spans="1:41">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" customFormat="1" hidden="1" spans="1:41">
+    <row r="7" customFormat="1" spans="1:41">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" customFormat="1" hidden="1" spans="1:41">
+    <row r="8" customFormat="1" spans="1:41">
       <c r="A8" s="2" t="s">
         <v>41</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" customFormat="1" hidden="1" spans="1:41">
+    <row r="9" customFormat="1" spans="1:41">
       <c r="A9" s="2" t="s">
         <v>41</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" customFormat="1" hidden="1" spans="1:41">
+    <row r="10" customFormat="1" spans="1:41">
       <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" customFormat="1" hidden="1" spans="1:41">
+    <row r="11" customFormat="1" spans="1:41">
       <c r="A11" s="2" t="s">
         <v>41</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" customFormat="1" hidden="1" spans="1:41">
+    <row r="12" customFormat="1" spans="1:41">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" customFormat="1" hidden="1" spans="1:41">
+    <row r="13" customFormat="1" spans="1:41">
       <c r="A13" s="2" t="s">
         <v>41</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" customFormat="1" hidden="1" spans="1:41">
+    <row r="14" customFormat="1" spans="1:41">
       <c r="A14" s="2" t="s">
         <v>41</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" customFormat="1" hidden="1" spans="1:41">
+    <row r="15" customFormat="1" spans="1:41">
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" customFormat="1" hidden="1" spans="1:41">
+    <row r="16" customFormat="1" spans="1:41">
       <c r="A16" s="2" t="s">
         <v>41</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" customFormat="1" hidden="1" spans="1:41">
+    <row r="17" customFormat="1" spans="1:41">
       <c r="A17" s="2" t="s">
         <v>41</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" customFormat="1" hidden="1" spans="1:41">
+    <row r="18" customFormat="1" spans="1:41">
       <c r="A18" s="2" t="s">
         <v>41</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" customFormat="1" hidden="1" spans="1:41">
+    <row r="19" customFormat="1" spans="1:41">
       <c r="A19" s="2" t="s">
         <v>41</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" customFormat="1" hidden="1" spans="1:41">
+    <row r="21" customFormat="1" spans="1:41">
       <c r="A21" s="2" t="s">
         <v>41</v>
       </c>
@@ -3790,12 +3790,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AO21" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="15">
-      <filters>
-        <filter val="SHG01"/>
-        <filter val="SHG19"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MU/Test upload format/SHG/2026 - 2027 - SHG/Q1 26-27  SHG.xlsx
+++ b/MU/Test upload format/SHG/2026 - 2027 - SHG/Q1 26-27  SHG.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AO$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AO$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="58">
   <si>
     <t>loancat</t>
   </si>
@@ -173,40 +173,37 @@
     <t>124 Main Street</t>
   </si>
   <si>
-    <t>603</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>SBIN0001235</t>
   </si>
   <si>
-    <t>SHG0124234</t>
-  </si>
-  <si>
-    <t>SHG01234</t>
+    <t>XSHG0124234</t>
+  </si>
+  <si>
+    <t>900001</t>
+  </si>
+  <si>
+    <t>01-04-2026</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>AQPPL2141K</t>
+  </si>
+  <si>
+    <t>1237</t>
+  </si>
+  <si>
+    <t>XSHG01234</t>
   </si>
   <si>
     <t>1000001</t>
   </si>
   <si>
-    <t>01-04-2026</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>AQPPL2141K</t>
-  </si>
-  <si>
-    <t>1237</t>
-  </si>
-  <si>
-    <t>651</t>
-  </si>
-  <si>
-    <t>SHG01234666</t>
+    <t>XSHG01234344</t>
+  </si>
+  <si>
+    <t>XSHG01234665</t>
   </si>
 </sst>
 </file>
@@ -863,7 +860,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
@@ -877,6 +874,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1228,8 +1226,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
+  <dimension ref="A1:AO4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="12.5714285714286" customWidth="1"/>
     <col min="2" max="2" width="18.5714285714286" customWidth="1"/>
@@ -1427,40 +1425,40 @@
       <c r="J2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="7">
         <v>209</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>48</v>
+      <c r="L2" s="7">
+        <v>233</v>
+      </c>
+      <c r="M2" s="7">
+        <v>10</v>
       </c>
       <c r="N2" s="2">
         <v>800026</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="T2" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="U2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="V2" s="7">
+        <v>50</v>
+      </c>
+      <c r="V2" s="8">
         <v>1000</v>
       </c>
       <c r="W2" s="2" t="s">
@@ -1482,16 +1480,16 @@
         <v>1</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>
-      <c r="AI2" s="7">
+      <c r="AI2" s="8">
         <v>1234567893</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AK2" s="2" t="s">
         <v>44</v>
@@ -1537,40 +1535,40 @@
       <c r="J3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="7">
         <v>209</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>48</v>
+      <c r="L3" s="7">
+        <v>233</v>
+      </c>
+      <c r="M3" s="7">
+        <v>10</v>
       </c>
       <c r="N3" s="2">
         <v>800026</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="T3" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="U3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="V3" s="7">
+        <v>50</v>
+      </c>
+      <c r="V3" s="8">
         <v>1000</v>
       </c>
       <c r="W3" s="2" t="s">
@@ -1589,32 +1587,136 @@
         <v>1</v>
       </c>
       <c r="AE3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI3" s="8">
+        <v>1234567893</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:41">
+      <c r="A4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" s="7">
+        <v>209</v>
+      </c>
+      <c r="L4" s="7">
+        <v>233</v>
+      </c>
+      <c r="M4" s="7">
+        <v>10</v>
+      </c>
+      <c r="N4" s="2">
+        <v>800026</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="AI3" s="7">
+      <c r="S4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="T4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="V4" s="8">
+        <v>1000</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI4" s="8">
         <v>1234567893</v>
       </c>
-      <c r="AJ3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO3" s="2" t="s">
+      <c r="AJ4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO4" s="2" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AO2" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AO3" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
